--- a/data/inputs/pre_lin_filt_OS_results.xlsx
+++ b/data/inputs/pre_lin_filt_OS_results.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://queensuca-my.sharepoint.com/personal/16mrf6_queensu_ca/Documents/Documents/Projects/NAT_pre/NAT_analysis/spatial_configuration_github/SCI/data/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_714DD2E74BF67CAA3BA20004682CF575653CF3CC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{627719F6-5A1A-4AAE-9355-0FC80969EE0A}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="11_714DD2E74BF67CAA3BA20004682CF575653CF3CC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CDAC0A89-85F2-4210-A584-3922EBBDAF3E}"/>
   <bookViews>
-    <workbookView xWindow="3780" yWindow="2145" windowWidth="23280" windowHeight="12480" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30795" yWindow="1950" windowWidth="23280" windowHeight="12480" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RankedCellData" sheetId="2" r:id="rId1"/>
     <sheet name="Weights" sheetId="3" r:id="rId2"/>
+    <sheet name="SampleIDs" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="108">
   <si>
     <t>Features</t>
   </si>
@@ -342,6 +343,9 @@
   </si>
   <si>
     <t>weight</t>
+  </si>
+  <si>
+    <t>sampleid</t>
   </si>
 </sst>
 </file>
@@ -9676,4 +9680,284 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C10096B7-965C-4AA2-A85E-84F11BED5ADC}">
+  <dimension ref="A1:A54"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>79</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>